--- a/fmradio/Macintosh/FM Radio.xlsx
+++ b/fmradio/Macintosh/FM Radio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoine/Documents/antoine/apple iigs/crossdevtools/sources/fmradio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoine/Documents/antoine/apple iigs/crossdevtools/source/fmradio/Macintosh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894AEA54-9507-1846-80AA-541EDD966AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866930FD-9E34-D542-A162-2EB1F24A73B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{2366F7C7-EDC6-1741-8107-033262854A0A}"/>
+    <workbookView xWindow="380" yWindow="620" windowWidth="28040" windowHeight="16940" xr2:uid="{2366F7C7-EDC6-1741-8107-033262854A0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -552,14 +552,14 @@
       </c>
       <c r="D1">
         <f>D2+SUM(D5:D16)</f>
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="str">
         <f>CONCATENATE(BIN2HEX(G2,2),BIN2HEX(G3,2))</f>
-        <v>0358</v>
+        <v>1B18</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -572,12 +572,15 @@
       <c r="D2">
         <v>-10700</v>
       </c>
+      <c r="E2">
+        <v>-10700</v>
+      </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="1" t="str">
         <f>CONCATENATE(C3,C4,C5,C6,C7,C8,C9,C10)</f>
-        <v>00000011</v>
+        <v>00011011</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -595,7 +598,7 @@
       </c>
       <c r="G3" s="1" t="str">
         <f>CONCATENATE(C11,C12,C13,C14,C15,C16,C17,C18)</f>
-        <v>01011000</v>
+        <v>00011000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -632,11 +635,11 @@
         <v>51200</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D16" si="0">IF(C6=1,B6,0)</f>
-        <v>0</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -647,11 +650,11 @@
         <v>25600</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -722,11 +725,11 @@
         <v>800</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">

--- a/fmradio/Macintosh/FM Radio.xlsx
+++ b/fmradio/Macintosh/FM Radio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoine/Documents/antoine/apple iigs/crossdevtools/source/fmradio/Macintosh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866930FD-9E34-D542-A162-2EB1F24A73B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91957E8E-616B-2B43-93F8-F33D7BA36356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="620" windowWidth="28040" windowHeight="16940" xr2:uid="{2366F7C7-EDC6-1741-8107-033262854A0A}"/>
   </bookViews>
@@ -552,14 +552,14 @@
       </c>
       <c r="D1">
         <f>D2+SUM(D5:D16)</f>
-        <v>76000</v>
+        <v>87500</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="str">
         <f>CONCATENATE(BIN2HEX(G2,2),BIN2HEX(G3,2))</f>
-        <v>1B18</v>
+        <v>1EB0</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -580,7 +580,7 @@
       </c>
       <c r="G2" s="1" t="str">
         <f>CONCATENATE(C3,C4,C5,C6,C7,C8,C9,C10)</f>
-        <v>00011011</v>
+        <v>00011110</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -598,7 +598,7 @@
       </c>
       <c r="G3" s="1" t="str">
         <f>CONCATENATE(C11,C12,C13,C14,C15,C16,C17,C18)</f>
-        <v>00011000</v>
+        <v>10110000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -665,11 +665,11 @@
         <v>12800</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12800</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -695,11 +695,11 @@
         <v>3200</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>3200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -710,11 +710,11 @@
         <v>1600</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -740,11 +740,11 @@
         <v>400</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -770,11 +770,11 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
